--- a/漢字（かんじ）/m.xlsx
+++ b/漢字（かんじ）/m.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ま" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="147">
   <si>
     <t>仮名</t>
   </si>
@@ -318,6 +318,7 @@
   <si>
     <t>国民｜こくみん
 民族｜みんぞく
+民主｜みんしゅ
 民間｜みんかん
 市民｜しみん</t>
   </si>
@@ -371,6 +372,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t xml:space="preserve">外務省｜がいむしょう
 </t>
     </r>
@@ -587,6 +594,12 @@
   <si>
     <t>猛獣｜もうじゅう</t>
   </si>
+  <si>
+    <t>耗</t>
+  </si>
+  <si>
+    <t>消耗｜しょうもう</t>
+  </si>
 </sst>
 </file>
 
@@ -598,7 +611,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,13 +643,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1086,148 +1092,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1929,7 +1935,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" ht="72" spans="1:7">
+    <row r="12" ht="90" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>72</v>
       </c>
@@ -2204,8 +2210,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="26.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="21.3333333333333" customWidth="1"/>
@@ -2350,6 +2356,17 @@
         <v>144</v>
       </c>
     </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/漢字（かんじ）/m.xlsx
+++ b/漢字（かんじ）/m.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="18288" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ま" sheetId="1" r:id="rId1"/>
@@ -475,7 +475,8 @@
   <si>
     <t>命運｜めいうん
 運命｜うんめい
-懸命｜けんめい</t>
+懸命｜けんめい
+宿命｜しゅくめい</t>
   </si>
   <si>
     <t>迷路｜めいろ
@@ -2157,7 +2158,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" ht="54" spans="1:3">
+    <row r="6" ht="72" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>105</v>
       </c>
